--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:48:59+00:00</t>
+    <t>2026-04-25T16:59:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:59:12+00:00</t>
+    <t>2026-04-25T17:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:20:31+00:00</t>
+    <t>2026-04-25T17:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/fhirpot-audit-event</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/StructureDefinition/fhirpot-audit-event</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,19 +63,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:34:35+00:00</t>
+    <t>2026-04-25T21:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ATTCK2FHIR IG</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ATTCK2FHIR IG (https://constir1.github.io/ATTCK2FHIR)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:04:27+00:00</t>
+    <t>2026-04-25T21:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:17:05+00:00</t>
+    <t>2026-04-25T21:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:19:40+00:00</t>
+    <t>2026-04-25T21:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:21:24+00:00</t>
+    <t>2026-04-26T14:57:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T14:57:42+00:00</t>
+    <t>2026-04-26T15:13:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:13:50+00:00</t>
+    <t>2026-04-26T15:44:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.3</t>
+    <t>0.0.04</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:44:08+00:00</t>
+    <t>2026-04-26T15:55:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.04</t>
+    <t>0.0.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:55:31+00:00</t>
+    <t>2026-04-26T20:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="368">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.5</t>
+    <t>0.0.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,19 +63,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T20:36:59+00:00</t>
+    <t>2026-05-14T08:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
     <t>ATTCK2FHIR IG</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ATTCK2FHIR IG (https://constir1.github.io/ATTCK2FHIR)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -481,22 +475,25 @@
     <t>This field enables queries of messages by implementation-defined event categories.</t>
   </si>
   <si>
+    <t>Sub-type of event.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type|4.0.1</t>
+  </si>
+  <si>
+    <t>AuditEvent.action</t>
+  </si>
+  <si>
+    <t>Type of action performed during the event</t>
+  </si>
+  <si>
+    <t>Indicator for type of action performed during the event that generated the audit.</t>
+  </si>
+  <si>
+    <t>This broadly indicates what kind of action was done on the AuditEvent.entity by the AuditEvent.agent.</t>
+  </si>
+  <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>http://example.org/fsh/ValueSet/MITRE-ATTCK-Techniques</t>
-  </si>
-  <si>
-    <t>AuditEvent.action</t>
-  </si>
-  <si>
-    <t>Type of action performed during the event</t>
-  </si>
-  <si>
-    <t>Indicator for type of action performed during the event that generated the audit.</t>
-  </si>
-  <si>
-    <t>This broadly indicates what kind of action was done on the AuditEvent.entity by the AuditEvent.agent.</t>
   </si>
   <si>
     <t>Indicator for type of action performed during the event that generated the event.</t>
@@ -584,7 +581,7 @@
     <t>Use AuditEvent.agent.purposeOfUse when you know that it is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
   </si>
   <si>
-    <t>http://example.org/fsh/ValueSet/MITRE-ATTCK-Tactics</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Tactics</t>
   </si>
   <si>
     <t>AuditEvent.agent</t>
@@ -1289,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1394,21 +1391,21 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>24</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -1448,14 +1445,6 @@
       </c>
       <c r="B20" t="s" s="2">
         <v>36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1483,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.12109375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="46.70703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="55.328125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1507,115 +1496,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>2</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>72</v>
-      </c>
-      <c r="AJ1" t="s" s="1">
-        <v>73</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -1623,104 +1612,104 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="H2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="I2" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s" s="2">
+      <c r="N2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="M2" t="s" s="2">
+      <c r="O2" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="O2" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -1728,104 +1717,104 @@
         <v>3</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L3" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="I3" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="O3" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1833,102 +1822,102 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N4" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -1936,104 +1925,104 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N5" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="O5" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -2041,104 +2030,104 @@
         <v>3</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="O6" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AA6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AB6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>110</v>
-      </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -2146,104 +2135,104 @@
         <v>3</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R7" s="2"/>
       <c r="S7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -2251,104 +2240,104 @@
         <v>3</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -2356,104 +2345,104 @@
         <v>3</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="O9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -2461,106 +2450,106 @@
         <v>3</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P10" t="s" s="2">
-        <v>136</v>
-      </c>
       <c r="Q10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -2568,104 +2557,104 @@
         <v>3</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AA11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="Z11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>145</v>
-      </c>
       <c r="AB11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -2673,102 +2662,104 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Z12" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="AA12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2776,104 +2767,104 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG13" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="AH13" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2881,104 +2872,104 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -2986,106 +2977,106 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="O15" t="s" s="2">
+      <c r="P15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="P15" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="Q15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R15" s="2"/>
       <c r="S15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -3093,104 +3084,104 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M16" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R16" s="2"/>
       <c r="S16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -3198,102 +3189,102 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R17" s="2"/>
       <c r="S17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -3301,102 +3292,102 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z18" s="2"/>
       <c r="AA18" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -3404,106 +3395,106 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="O19" t="s" s="2">
+      <c r="P19" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="P19" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="Q19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -3511,102 +3502,102 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M20" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -3614,104 +3605,104 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -3719,106 +3710,106 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M22" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="O22" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P22" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R22" s="2"/>
       <c r="S22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23">
@@ -3826,102 +3817,102 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R23" s="2"/>
       <c r="S23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AA23" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AB23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
@@ -3929,106 +3920,106 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O24" t="s" s="2">
+      <c r="P24" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="P24" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="Q24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R24" s="2"/>
       <c r="S24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="AB24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -4036,106 +4027,106 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="O25" t="s" s="2">
+      <c r="P25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="P25" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="Q25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R25" s="2"/>
       <c r="S25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26">
@@ -4143,104 +4134,104 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M26" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R26" s="2"/>
       <c r="S26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27">
@@ -4248,104 +4239,104 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M27" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R27" s="2"/>
       <c r="S27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
@@ -4353,106 +4344,106 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="O28" t="s" s="2">
+      <c r="P28" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="P28" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="Q28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R28" s="2"/>
       <c r="S28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
@@ -4460,102 +4451,102 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
@@ -4563,106 +4554,106 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M30" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="O30" t="s" s="2">
+      <c r="P30" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="P30" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="Q30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31">
@@ -4670,104 +4661,104 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z31" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AA31" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AA31" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AB31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32">
@@ -4775,102 +4766,102 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R32" s="2"/>
       <c r="S32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33">
@@ -4878,102 +4869,102 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R33" s="2"/>
       <c r="S33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -4981,104 +4972,104 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R34" s="2"/>
       <c r="S34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
@@ -5086,106 +5077,106 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36">
@@ -5193,106 +5184,106 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="O36" t="s" s="2">
+      <c r="P36" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="P36" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="Q36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -5300,104 +5291,104 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R37" s="2"/>
       <c r="S37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Z37" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA37" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="AB37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
@@ -5405,104 +5396,104 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R38" s="2"/>
       <c r="S38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA38" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AB38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39">
@@ -5510,106 +5501,106 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M39" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O39" t="s" s="2">
+      <c r="P39" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="P39" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="Q39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40">
@@ -5617,102 +5608,102 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M40" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R40" s="2"/>
       <c r="S40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -5720,104 +5711,104 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42">
@@ -5825,106 +5816,106 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="O42" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R42" s="2"/>
       <c r="S42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43">
@@ -5932,104 +5923,104 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R43" s="2"/>
       <c r="S43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
@@ -6037,104 +6028,104 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R44" s="2"/>
       <c r="S44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45">
@@ -6142,104 +6133,104 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R45" s="2"/>
       <c r="S45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z45" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA45" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AA45" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AB45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46">
@@ -6247,106 +6238,106 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="O46" t="s" s="2">
+      <c r="P46" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="P46" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="Q46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R46" s="2"/>
       <c r="S46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47">
@@ -6354,102 +6345,102 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R47" s="2"/>
       <c r="S47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -6457,104 +6448,104 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R48" s="2"/>
       <c r="S48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49">
@@ -6562,106 +6553,106 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R49" s="2"/>
       <c r="S49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
@@ -6669,102 +6660,102 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R50" s="2"/>
       <c r="S50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
@@ -6772,106 +6763,106 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="O51" t="s" s="2">
+      <c r="P51" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="P51" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="Q51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R51" s="2"/>
       <c r="S51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AA51" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AB51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52">
@@ -6879,104 +6870,104 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R52" s="2"/>
       <c r="S52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AA52" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AA52" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AB52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53">
@@ -6984,106 +6975,106 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="O53" t="s" s="2">
+      <c r="P53" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="P53" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="Q53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R53" s="2"/>
       <c r="S53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54">
@@ -7091,106 +7082,106 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="O54" t="s" s="2">
+      <c r="P54" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="P54" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="Q54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R54" s="2"/>
       <c r="S54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z54" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AA54" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AA54" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AB54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55">
@@ -7198,106 +7189,106 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="O55" t="s" s="2">
+      <c r="P55" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="P55" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="Q55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R55" s="2"/>
       <c r="S55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56">
@@ -7305,104 +7296,104 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R56" s="2"/>
       <c r="S56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57">
@@ -7410,106 +7401,106 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="O57" t="s" s="2">
+      <c r="P57" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="P57" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="Q57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R57" s="2"/>
       <c r="S57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
@@ -7517,104 +7508,104 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R58" s="2"/>
       <c r="S58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
@@ -7622,102 +7613,102 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R59" s="2"/>
       <c r="S59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -7725,104 +7716,104 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61">
@@ -7830,106 +7821,106 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P61" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R61" s="2"/>
       <c r="S61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62">
@@ -7937,102 +7928,102 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R62" s="2"/>
       <c r="S62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63">
@@ -8040,106 +8031,106 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="O63" t="s" s="2">
+      <c r="P63" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="P63" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="Q63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R63" s="2"/>
       <c r="S63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.6</t>
+    <t>0.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:02:20+00:00</t>
+    <t>2026-05-14T08:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.7</t>
+    <t>0.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:13:13+00:00</t>
+    <t>2026-05-14T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AuditEvent profile for FHIR honeypot detections with MITRE ATT&amp;CK and OWASP</t>
+    <t>AuditEvent profile for FHIR honeypot detections, classifying events with MITRE ATT&amp;CK tactics, techniques, and (optionally) subtechniques.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -445,42 +445,85 @@
 </t>
   </si>
   <si>
-    <t>Type/identifier of event</t>
-  </si>
-  <si>
-    <t>Identifier for a family of the event.  For example, a menu item, program, rule, policy, function code, application name or URL. It identifies the performed function.</t>
+    <t>MITRE ATT&amp;CK Tactic associated with the technique</t>
+  </si>
+  <si>
+    <t>The MITRE ATT&amp;CK tactic this event maps to. SHALL be one of the tactic codes listed on the technique referenced in AuditEvent.subtype[technique] via the MITRE-ATTCK-Techniques CodeSystem's `tactic` property. This profile does not enforce the cross-element linkage with a FHIRPath invariant because R4 cannot portably read CodeSystem properties from FHIRPath; implementers are responsible for the linkage.</t>
   </si>
   <si>
     <t>This identifies the performed function. For "Execute" Event Action Code audit records, this identifies the application function performed.</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Tactics</t>
+  </si>
+  <si>
+    <t>AuditEvent.subtype</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>More specific type/id for the event</t>
+  </si>
+  <si>
+    <t>Identifier for the category of event.</t>
+  </si>
+  <si>
+    <t>This field enables queries of messages by implementation-defined event categories.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>Type of event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-type|4.0.1</t>
-  </si>
-  <si>
-    <t>AuditEvent.subtype</t>
-  </si>
-  <si>
-    <t>More specific type/id for the event</t>
-  </si>
-  <si>
-    <t>Identifier for the category of event.</t>
-  </si>
-  <si>
-    <t>This field enables queries of messages by implementation-defined event categories.</t>
-  </si>
-  <si>
     <t>Sub-type of event.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>First entry is the MITRE ATT&amp;CK technique; an optional second entry refines it to a subtechnique of that technique.</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>AuditEvent.subtype:technique</t>
+  </si>
+  <si>
+    <t>technique</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK Technique (parent)</t>
+  </si>
+  <si>
+    <t>The MITRE ATT&amp;CK parent technique (e.g. T1037). Exactly one is required per event.</t>
+  </si>
+  <si>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Parent-Techniques</t>
+  </si>
+  <si>
+    <t>AuditEvent.subtype:subtechnique</t>
+  </si>
+  <si>
+    <t>subtechnique</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK Subtechnique (optional refinement)</t>
+  </si>
+  <si>
+    <t>An optional MITRE ATT&amp;CK subtechnique (e.g. T1037.004) that refines subtype[technique]. SHALL be a subtechnique whose `parentTechnique` property points to the code in subtype[technique] — not enforced here for the same reason given on `type`.</t>
+  </si>
+  <si>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Subtechniques</t>
+  </si>
+  <si>
     <t>AuditEvent.action</t>
   </si>
   <si>
@@ -491,9 +534,6 @@
   </si>
   <si>
     <t>This broadly indicates what kind of action was done on the AuditEvent.entity by the AuditEvent.agent.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>Indicator for type of action performed during the event that generated the event.</t>
@@ -581,7 +621,10 @@
     <t>Use AuditEvent.agent.purposeOfUse when you know that it is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
   </si>
   <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Tactics</t>
+    <t>The reason the activity took place.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
     <t>AuditEvent.agent</t>
@@ -858,12 +901,6 @@
   </si>
   <si>
     <t>Use AuditEvent.agent.purposeOfUse when you know that is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
-  </si>
-  <si>
-    <t>The reason the activity took place.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
     <t>AuditEvent.source</t>
@@ -1454,13 +1491,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK63"/>
+  <dimension ref="A1:AK65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.72265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.1875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="36.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="11.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1483,10 +1520,10 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.12109375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="55.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="64.5078125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="91.64453125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2620,11 +2657,9 @@
       <c r="Y11" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="Z11" t="s" s="2">
+      <c r="Z11" s="2"/>
+      <c r="AA11" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="AB11" t="s" s="2">
         <v>20</v>
@@ -2662,10 +2697,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -2673,10 +2708,10 @@
       </c>
       <c r="F12" s="2"/>
       <c r="G12" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2723,31 +2758,31 @@
         <v>20</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AE12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>73</v>
@@ -2767,18 +2802,20 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="E13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -2793,17 +2830,17 @@
         <v>82</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="Q13" t="s" s="2">
         <v>20</v>
@@ -2828,13 +2865,11 @@
         <v>20</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Z13" s="2"/>
       <c r="AA13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AB13" t="s" s="2">
         <v>20</v>
@@ -2852,13 +2887,13 @@
         <v>20</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>20</v>
@@ -2872,12 +2907,14 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="E14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2895,21 +2932,21 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="P14" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="Q14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2933,13 +2970,11 @@
         <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Z14" s="2"/>
       <c r="AA14" t="s" s="2">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="AB14" t="s" s="2">
         <v>20</v>
@@ -2957,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>20</v>
@@ -2977,10 +3012,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -2988,7 +3023,7 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
@@ -3003,17 +3038,15 @@
         <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>167</v>
       </c>
@@ -3040,13 +3073,13 @@
         <v>20</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AB15" t="s" s="2">
         <v>20</v>
@@ -3064,10 +3097,10 @@
         <v>20</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -3084,10 +3117,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3107,19 +3140,19 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
@@ -3145,31 +3178,31 @@
         <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG16" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>73</v>
@@ -3189,10 +3222,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3200,7 +3233,7 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3215,16 +3248,20 @@
         <v>82</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="P17" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="Q17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3272,10 +3309,10 @@
         <v>20</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -3292,10 +3329,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3306,7 +3343,7 @@
         <v>73</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3318,16 +3355,16 @@
         <v>82</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
@@ -3355,9 +3392,11 @@
       <c r="Y18" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="Z18" s="2"/>
+      <c r="Z18" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="AA18" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AB18" t="s" s="2">
         <v>20</v>
@@ -3375,13 +3414,13 @@
         <v>20</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>20</v>
@@ -3395,21 +3434,21 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -3418,23 +3457,19 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="P19" t="s" s="2">
         <v>189</v>
       </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3482,13 +3517,13 @@
         <v>20</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>20</v>
@@ -3516,7 +3551,7 @@
         <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
@@ -3525,18 +3560,20 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
         <v>20</v>
@@ -3561,13 +3598,13 @@
         <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="AB20" t="s" s="2">
         <v>20</v>
@@ -3585,19 +3622,19 @@
         <v>20</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
@@ -3605,18 +3642,18 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -3631,18 +3668,20 @@
         <v>20</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P21" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="Q21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3690,10 +3729,10 @@
         <v>20</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -3702,7 +3741,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
@@ -3710,46 +3749,42 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
         <v>20</v>
       </c>
@@ -3797,19 +3832,19 @@
         <v>20</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -3817,21 +3852,21 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -3843,15 +3878,17 @@
         <v>20</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
         <v>20</v>
@@ -3876,13 +3913,13 @@
         <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
         <v>20</v>
@@ -3900,19 +3937,19 @@
         <v>20</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24">
@@ -3920,14 +3957,14 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -3940,25 +3977,25 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="Q24" t="s" s="2">
         <v>20</v>
@@ -3983,13 +4020,13 @@
         <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
         <v>20</v>
@@ -4007,7 +4044,7 @@
         <v>20</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>73</v>
@@ -4019,7 +4056,7 @@
         <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
@@ -4027,14 +4064,14 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
@@ -4050,23 +4087,19 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4090,13 +4123,13 @@
         <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="AB25" t="s" s="2">
         <v>20</v>
@@ -4114,7 +4147,7 @@
         <v>20</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>73</v>
@@ -4134,10 +4167,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4148,7 +4181,7 @@
         <v>73</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4160,15 +4193,17 @@
         <v>20</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="M26" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>225</v>
       </c>
@@ -4195,13 +4230,13 @@
         <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AB26" t="s" s="2">
         <v>20</v>
@@ -4219,13 +4254,13 @@
         <v>20</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>20</v>
@@ -4239,14 +4274,14 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
@@ -4262,20 +4297,22 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P27" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q27" t="s" s="2">
         <v>20</v>
@@ -4324,7 +4361,7 @@
         <v>20</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>73</v>
@@ -4344,10 +4381,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4355,7 +4392,7 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -4367,22 +4404,20 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>20</v>
@@ -4431,10 +4466,10 @@
         <v>20</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
@@ -4451,10 +4486,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4477,16 +4512,18 @@
         <v>20</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>237</v>
+        <v>187</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="Q29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4534,7 +4571,7 @@
         <v>20</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>73</v>
@@ -4554,10 +4591,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4565,10 +4602,10 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4577,22 +4614,22 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>95</v>
+        <v>245</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>20</v>
@@ -4641,13 +4678,13 @@
         <v>20</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>20</v>
@@ -4661,10 +4698,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4687,18 +4724,16 @@
         <v>20</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
         <v>20</v>
       </c>
@@ -4722,31 +4757,31 @@
         <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG31" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>73</v>
@@ -4766,10 +4801,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -4780,7 +4815,7 @@
         <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -4792,16 +4827,20 @@
         <v>20</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="Q32" t="s" s="2">
         <v>20</v>
       </c>
@@ -4849,13 +4888,13 @@
         <v>20</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>20</v>
@@ -4869,10 +4908,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -4895,16 +4934,18 @@
         <v>20</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="Q33" t="s" s="2">
         <v>20</v>
       </c>
@@ -4928,13 +4969,13 @@
         <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="AB33" t="s" s="2">
         <v>20</v>
@@ -4952,7 +4993,7 @@
         <v>20</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>73</v>
@@ -4964,7 +5005,7 @@
         <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
@@ -4972,21 +5013,21 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
@@ -4998,17 +5039,15 @@
         <v>20</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
         <v>20</v>
@@ -5057,19 +5096,19 @@
         <v>20</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
@@ -5077,46 +5116,42 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5164,19 +5199,19 @@
         <v>20</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -5184,21 +5219,21 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -5210,20 +5245,18 @@
         <v>20</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>259</v>
+        <v>209</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="P36" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5271,19 +5304,19 @@
         <v>20</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37">
@@ -5291,43 +5324,45 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P37" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="Q37" t="s" s="2">
         <v>20</v>
@@ -5352,13 +5387,13 @@
         <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
         <v>20</v>
@@ -5376,19 +5411,19 @@
         <v>20</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38">
@@ -5396,10 +5431,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5410,7 +5445,7 @@
         <v>73</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -5422,18 +5457,20 @@
         <v>20</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="P38" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="Q38" t="s" s="2">
         <v>20</v>
       </c>
@@ -5457,13 +5494,13 @@
         <v>20</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
         <v>20</v>
@@ -5481,13 +5518,13 @@
         <v>20</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>20</v>
@@ -5501,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5512,7 +5549,7 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -5527,19 +5564,17 @@
         <v>20</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>20</v>
@@ -5564,13 +5599,13 @@
         <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="AB39" t="s" s="2">
         <v>20</v>
@@ -5588,10 +5623,10 @@
         <v>20</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -5608,10 +5643,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5622,7 +5657,7 @@
         <v>73</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -5634,15 +5669,17 @@
         <v>20</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>191</v>
+        <v>283</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P40" s="2"/>
       <c r="Q40" t="s" s="2">
         <v>20</v>
@@ -5667,13 +5704,13 @@
         <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="AB40" t="s" s="2">
         <v>20</v>
@@ -5691,19 +5728,19 @@
         <v>20</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41">
@@ -5711,21 +5748,21 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
@@ -5737,18 +5774,20 @@
         <v>20</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P41" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="Q41" t="s" s="2">
         <v>20</v>
       </c>
@@ -5796,19 +5835,19 @@
         <v>20</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
@@ -5816,46 +5855,42 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
         <v>20</v>
       </c>
@@ -5903,19 +5938,19 @@
         <v>20</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -5923,21 +5958,21 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -5949,18 +5984,18 @@
         <v>20</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>283</v>
+        <v>126</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6008,19 +6043,19 @@
         <v>20</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>282</v>
+        <v>210</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
@@ -6028,43 +6063,45 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>217</v>
+        <v>125</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>288</v>
+        <v>213</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P44" t="s" s="2">
-        <v>290</v>
+        <v>134</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>20</v>
@@ -6113,19 +6150,19 @@
         <v>20</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>286</v>
+        <v>215</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
@@ -6133,10 +6170,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6147,7 +6184,7 @@
         <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -6159,17 +6196,17 @@
         <v>20</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>20</v>
@@ -6194,13 +6231,13 @@
         <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
         <v>20</v>
@@ -6218,13 +6255,13 @@
         <v>20</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>20</v>
@@ -6238,21 +6275,21 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -6261,20 +6298,18 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O46" t="s" s="2">
         <v>301</v>
       </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>302</v>
       </c>
@@ -6325,19 +6360,19 @@
         <v>20</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>303</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47">
@@ -6345,10 +6380,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6359,7 +6394,7 @@
         <v>73</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -6371,16 +6406,18 @@
         <v>20</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>191</v>
+        <v>304</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="Q47" t="s" s="2">
         <v>20</v>
       </c>
@@ -6404,13 +6441,13 @@
         <v>20</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>20</v>
@@ -6428,19 +6465,19 @@
         <v>20</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48">
@@ -6448,14 +6485,14 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>124</v>
+        <v>310</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
@@ -6474,18 +6511,20 @@
         <v>20</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P48" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="Q48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6533,7 +6572,7 @@
         <v>20</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>73</v>
@@ -6545,7 +6584,7 @@
         <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>130</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49">
@@ -6553,46 +6592,42 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
         <v>20</v>
       </c>
@@ -6640,19 +6675,19 @@
         <v>20</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -6660,21 +6695,21 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -6683,18 +6718,20 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>308</v>
+        <v>125</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>309</v>
+        <v>126</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
         <v>20</v>
@@ -6743,19 +6780,19 @@
         <v>20</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>307</v>
+        <v>210</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51">
@@ -6763,45 +6800,45 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>312</v>
+        <v>213</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>313</v>
+        <v>214</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>314</v>
+        <v>128</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>315</v>
+        <v>134</v>
       </c>
       <c r="Q51" t="s" s="2">
         <v>20</v>
@@ -6826,13 +6863,13 @@
         <v>20</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
         <v>20</v>
@@ -6850,19 +6887,19 @@
         <v>20</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52">
@@ -6870,10 +6907,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -6893,21 +6930,19 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
         <v>20</v>
       </c>
@@ -6931,13 +6966,13 @@
         <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="AB52" t="s" s="2">
         <v>20</v>
@@ -6955,7 +6990,7 @@
         <v>20</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>73</v>
@@ -6975,10 +7010,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7004,16 +7039,16 @@
         <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="O53" t="s" s="2">
+      <c r="P53" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>20</v>
@@ -7038,10 +7073,10 @@
         <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>329</v>
@@ -7062,7 +7097,7 @@
         <v>20</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>73</v>
@@ -7096,7 +7131,7 @@
         <v>73</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
@@ -7116,11 +7151,9 @@
       <c r="N54" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="O54" t="s" s="2">
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="Q54" t="s" s="2">
         <v>20</v>
@@ -7145,13 +7178,13 @@
         <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Z54" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA54" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AB54" t="s" s="2">
         <v>20</v>
@@ -7175,7 +7208,7 @@
         <v>73</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>20</v>
@@ -7189,10 +7222,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7212,22 +7245,22 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="O55" t="s" s="2">
+      <c r="P55" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>20</v>
@@ -7252,13 +7285,13 @@
         <v>20</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="AB55" t="s" s="2">
         <v>20</v>
@@ -7276,7 +7309,7 @@
         <v>20</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>73</v>
@@ -7285,7 +7318,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>93</v>
@@ -7296,10 +7329,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7310,7 +7343,7 @@
         <v>73</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -7322,17 +7355,19 @@
         <v>20</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>20</v>
@@ -7357,13 +7392,13 @@
         <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="AB56" t="s" s="2">
         <v>20</v>
@@ -7381,13 +7416,13 @@
         <v>20</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>20</v>
@@ -7401,10 +7436,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -7427,19 +7462,19 @@
         <v>82</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>347</v>
+        <v>187</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P57" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>20</v>
@@ -7488,7 +7523,7 @@
         <v>20</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>73</v>
@@ -7497,7 +7532,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>93</v>
@@ -7508,10 +7543,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -7522,7 +7557,7 @@
         <v>73</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -7534,17 +7569,17 @@
         <v>20</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q58" t="s" s="2">
         <v>20</v>
@@ -7593,13 +7628,13 @@
         <v>20</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>20</v>
@@ -7613,10 +7648,10 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -7636,19 +7671,23 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>174</v>
+        <v>359</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>191</v>
+        <v>360</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="Q59" t="s" s="2">
         <v>20</v>
       </c>
@@ -7696,7 +7735,7 @@
         <v>20</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>193</v>
+        <v>358</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>73</v>
@@ -7705,10 +7744,10 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
@@ -7716,14 +7755,14 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
@@ -7742,18 +7781,18 @@
         <v>20</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>126</v>
+        <v>365</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P60" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="Q60" t="s" s="2">
         <v>20</v>
       </c>
@@ -7801,7 +7840,7 @@
         <v>20</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>196</v>
+        <v>364</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>73</v>
@@ -7813,7 +7852,7 @@
         <v>20</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61">
@@ -7821,46 +7860,42 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
         <v>20</v>
       </c>
@@ -7908,19 +7943,19 @@
         <v>20</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -7928,21 +7963,21 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>20</v>
@@ -7954,15 +7989,17 @@
         <v>20</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>360</v>
+        <v>126</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
         <v>20</v>
@@ -8011,19 +8048,19 @@
         <v>20</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>359</v>
+        <v>210</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63">
@@ -8031,45 +8068,45 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>363</v>
+        <v>125</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>364</v>
+        <v>213</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>365</v>
+        <v>214</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>366</v>
+        <v>128</v>
       </c>
       <c r="P63" t="s" s="2">
-        <v>367</v>
+        <v>134</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>20</v>
@@ -8118,18 +8155,228 @@
         <v>20</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>362</v>
+        <v>215</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R64" s="2"/>
+      <c r="S64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R65" s="2"/>
+      <c r="S65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>93</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.8</t>
+    <t>0.0.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T10:01:26+00:00</t>
+    <t>2026-05-14T18:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="366">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.9</t>
+    <t>0.0.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T18:17:12+00:00</t>
+    <t>2026-05-15T18:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -466,62 +466,16 @@
     <t>2</t>
   </si>
   <si>
-    <t>More specific type/id for the event</t>
-  </si>
-  <si>
-    <t>Identifier for the category of event.</t>
+    <t>MITRE ATT&amp;CK Technique (parent), with optional subtechnique refinement</t>
+  </si>
+  <si>
+    <t>1..2 MITRE ATT&amp;CK technique codes. By convention the first entry is the parent technique (e.g. T1037) and the optional second entry is a subtechnique that refines it (e.g. T1037.004). This profile does not enforce slot order or the parent-subtechnique linkage at the FHIRPath layer because R4 discriminators cannot express ValueSet-based slicing; implementers are responsible for the ordering and the linkage.</t>
   </si>
   <si>
     <t>This field enables queries of messages by implementation-defined event categories.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Sub-type of event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>First entry is the MITRE ATT&amp;CK technique; an optional second entry refines it to a subtechnique of that technique.</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>AuditEvent.subtype:technique</t>
-  </si>
-  <si>
-    <t>technique</t>
-  </si>
-  <si>
-    <t>MITRE ATT&amp;CK Technique (parent)</t>
-  </si>
-  <si>
-    <t>The MITRE ATT&amp;CK parent technique (e.g. T1037). Exactly one is required per event.</t>
-  </si>
-  <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Parent-Techniques</t>
-  </si>
-  <si>
-    <t>AuditEvent.subtype:subtechnique</t>
-  </si>
-  <si>
-    <t>subtechnique</t>
-  </si>
-  <si>
-    <t>MITRE ATT&amp;CK Subtechnique (optional refinement)</t>
-  </si>
-  <si>
-    <t>An optional MITRE ATT&amp;CK subtechnique (e.g. T1037.004) that refines subtype[technique]. SHALL be a subtechnique whose `parentTechnique` property points to the code in subtype[technique] — not enforced here for the same reason given on `type`.</t>
-  </si>
-  <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Subtechniques</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Techniques</t>
   </si>
   <si>
     <t>AuditEvent.action</t>
@@ -619,6 +573,9 @@
   </si>
   <si>
     <t>Use AuditEvent.agent.purposeOfUse when you know that it is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>The reason the activity took place.</t>
@@ -1491,13 +1448,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK65"/>
+  <dimension ref="A1:AK63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.72265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.1875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="36.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="11.546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1520,10 +1477,10 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.12109375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="64.5078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="58.8046875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="91.64453125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2758,28 +2715,26 @@
         <v>20</v>
       </c>
       <c r="Y12" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="Z12" s="2"/>
+      <c r="AA12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="Z12" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>150</v>
-      </c>
       <c r="AB12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>143</v>
@@ -2802,20 +2757,18 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -2830,17 +2783,17 @@
         <v>82</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="Q13" t="s" s="2">
         <v>20</v>
@@ -2867,9 +2820,11 @@
       <c r="Y13" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="Z13" s="2"/>
+      <c r="Z13" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="AA13" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AB13" t="s" s="2">
         <v>20</v>
@@ -2887,13 +2842,13 @@
         <v>20</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>20</v>
@@ -2907,14 +2862,12 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2932,21 +2885,21 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="P14" s="2"/>
       <c r="Q14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2970,11 +2923,13 @@
         <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="Z14" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AA14" t="s" s="2">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
         <v>20</v>
@@ -2992,13 +2947,13 @@
         <v>20</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>20</v>
@@ -3012,10 +2967,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3023,7 +2978,7 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
@@ -3038,17 +2993,19 @@
         <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="M15" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="P15" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="Q15" t="s" s="2">
         <v>20</v>
@@ -3073,13 +3030,13 @@
         <v>20</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
         <v>20</v>
@@ -3097,10 +3054,10 @@
         <v>20</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -3117,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3140,19 +3097,19 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
@@ -3178,13 +3135,13 @@
         <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AB16" t="s" s="2">
         <v>20</v>
@@ -3202,7 +3159,7 @@
         <v>20</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>73</v>
@@ -3222,10 +3179,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3233,7 +3190,7 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3248,20 +3205,16 @@
         <v>82</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="P17" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
       <c r="Q17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3309,10 +3262,10 @@
         <v>20</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -3329,10 +3282,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3343,7 +3296,7 @@
         <v>73</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3355,16 +3308,16 @@
         <v>82</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
@@ -3390,13 +3343,13 @@
         <v>20</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AB18" t="s" s="2">
         <v>20</v>
@@ -3414,13 +3367,13 @@
         <v>20</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>20</v>
@@ -3434,21 +3387,21 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -3457,19 +3410,23 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="P19" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3517,13 +3474,13 @@
         <v>20</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>20</v>
@@ -3551,7 +3508,7 @@
         <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
@@ -3560,20 +3517,18 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>194</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
         <v>20</v>
@@ -3598,13 +3553,13 @@
         <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
         <v>20</v>
@@ -3622,19 +3577,19 @@
         <v>20</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -3642,18 +3597,18 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -3668,20 +3623,18 @@
         <v>20</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3729,10 +3682,10 @@
         <v>20</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -3741,7 +3694,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -3749,42 +3702,46 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q22" t="s" s="2">
         <v>20</v>
       </c>
@@ -3832,19 +3789,19 @@
         <v>20</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23">
@@ -3852,21 +3809,21 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -3878,17 +3835,15 @@
         <v>20</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
         <v>20</v>
@@ -3913,13 +3868,13 @@
         <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AB23" t="s" s="2">
         <v>20</v>
@@ -3937,19 +3892,19 @@
         <v>20</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
@@ -3957,14 +3912,14 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -3977,25 +3932,25 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="Q24" t="s" s="2">
         <v>20</v>
@@ -4020,13 +3975,13 @@
         <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="AB24" t="s" s="2">
         <v>20</v>
@@ -4044,7 +3999,7 @@
         <v>20</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>73</v>
@@ -4056,7 +4011,7 @@
         <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -4064,14 +4019,14 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
@@ -4087,19 +4042,23 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="P25" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="Q25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4123,13 +4082,13 @@
         <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
         <v>20</v>
@@ -4147,7 +4106,7 @@
         <v>20</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>73</v>
@@ -4167,10 +4126,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4181,7 +4140,7 @@
         <v>73</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4193,17 +4152,15 @@
         <v>20</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O26" t="s" s="2">
         <v>224</v>
       </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>225</v>
       </c>
@@ -4230,13 +4187,13 @@
         <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
         <v>20</v>
@@ -4254,13 +4211,13 @@
         <v>20</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>20</v>
@@ -4274,14 +4231,14 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
@@ -4297,22 +4254,20 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="Q27" t="s" s="2">
         <v>20</v>
@@ -4361,7 +4316,7 @@
         <v>20</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>73</v>
@@ -4381,10 +4336,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4392,7 +4347,7 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -4404,20 +4359,22 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P28" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>20</v>
@@ -4466,10 +4423,10 @@
         <v>20</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
@@ -4486,10 +4443,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4512,18 +4469,16 @@
         <v>20</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>243</v>
-      </c>
+      <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4571,7 +4526,7 @@
         <v>20</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>73</v>
@@ -4591,10 +4546,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4602,10 +4557,10 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4614,22 +4569,22 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>245</v>
+        <v>95</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>20</v>
@@ -4678,13 +4633,13 @@
         <v>20</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>20</v>
@@ -4698,10 +4653,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4724,16 +4679,18 @@
         <v>20</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>251</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="Q31" t="s" s="2">
         <v>20</v>
       </c>
@@ -4757,13 +4714,13 @@
         <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AB31" t="s" s="2">
         <v>20</v>
@@ -4781,7 +4738,7 @@
         <v>20</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>73</v>
@@ -4801,10 +4758,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -4815,7 +4772,7 @@
         <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -4827,20 +4784,16 @@
         <v>20</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
         <v>20</v>
       </c>
@@ -4888,13 +4841,13 @@
         <v>20</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>20</v>
@@ -4908,10 +4861,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -4934,18 +4887,16 @@
         <v>20</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>192</v>
       </c>
       <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>262</v>
-      </c>
+      <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
         <v>20</v>
       </c>
@@ -4969,13 +4920,13 @@
         <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
         <v>20</v>
@@ -4993,7 +4944,7 @@
         <v>20</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>73</v>
@@ -5005,7 +4956,7 @@
         <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -5013,21 +4964,21 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
@@ -5039,15 +4990,17 @@
         <v>20</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>266</v>
+        <v>126</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
         <v>20</v>
@@ -5096,19 +5049,19 @@
         <v>20</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
@@ -5116,42 +5069,46 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5199,19 +5156,19 @@
         <v>20</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36">
@@ -5219,21 +5176,21 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -5245,18 +5202,20 @@
         <v>20</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>126</v>
+        <v>258</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P36" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="Q36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5304,19 +5263,19 @@
         <v>20</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -5324,45 +5283,43 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>134</v>
+        <v>265</v>
       </c>
       <c r="Q37" t="s" s="2">
         <v>20</v>
@@ -5387,13 +5344,13 @@
         <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="AB37" t="s" s="2">
         <v>20</v>
@@ -5411,19 +5368,19 @@
         <v>20</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
@@ -5431,10 +5388,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5445,7 +5402,7 @@
         <v>73</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -5457,20 +5414,18 @@
         <v>20</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="P38" s="2"/>
       <c r="Q38" t="s" s="2">
         <v>20</v>
       </c>
@@ -5494,13 +5449,13 @@
         <v>20</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="AB38" t="s" s="2">
         <v>20</v>
@@ -5518,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>20</v>
@@ -5538,10 +5493,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5549,7 +5504,7 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -5564,17 +5519,19 @@
         <v>20</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P39" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>20</v>
@@ -5599,13 +5556,13 @@
         <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
         <v>20</v>
@@ -5623,10 +5580,10 @@
         <v>20</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -5643,10 +5600,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5657,7 +5614,7 @@
         <v>73</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -5669,17 +5626,15 @@
         <v>20</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="N40" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" t="s" s="2">
         <v>20</v>
@@ -5704,13 +5659,13 @@
         <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
         <v>20</v>
@@ -5728,19 +5683,19 @@
         <v>20</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>282</v>
+        <v>193</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -5748,21 +5703,21 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
@@ -5774,20 +5729,18 @@
         <v>20</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>126</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>288</v>
+        <v>195</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
         <v>20</v>
       </c>
@@ -5835,19 +5788,19 @@
         <v>20</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42">
@@ -5855,42 +5808,46 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q42" t="s" s="2">
         <v>20</v>
       </c>
@@ -5938,19 +5895,19 @@
         <v>20</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43">
@@ -5958,21 +5915,21 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -5984,18 +5941,18 @@
         <v>20</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P43" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="Q43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6043,19 +6000,19 @@
         <v>20</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
@@ -6063,45 +6020,43 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>213</v>
+        <v>286</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>134</v>
+        <v>288</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>20</v>
@@ -6150,19 +6105,19 @@
         <v>20</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45">
@@ -6170,10 +6125,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6184,7 +6139,7 @@
         <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -6196,17 +6151,17 @@
         <v>20</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>20</v>
@@ -6231,13 +6186,13 @@
         <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AB45" t="s" s="2">
         <v>20</v>
@@ -6255,13 +6210,13 @@
         <v>20</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>20</v>
@@ -6275,21 +6230,21 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -6298,20 +6253,22 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="P46" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>20</v>
@@ -6360,19 +6317,19 @@
         <v>20</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>93</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47">
@@ -6380,10 +6337,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6394,7 +6351,7 @@
         <v>73</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -6406,18 +6363,16 @@
         <v>20</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>304</v>
+        <v>191</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>305</v>
+        <v>192</v>
       </c>
       <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
         <v>20</v>
       </c>
@@ -6441,13 +6396,13 @@
         <v>20</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>20</v>
@@ -6465,19 +6420,19 @@
         <v>20</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -6485,14 +6440,14 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>310</v>
+        <v>124</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
@@ -6511,20 +6466,18 @@
         <v>20</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>126</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6572,7 +6525,7 @@
         <v>20</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>73</v>
@@ -6584,7 +6537,7 @@
         <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>315</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49">
@@ -6592,42 +6545,46 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q49" t="s" s="2">
         <v>20</v>
       </c>
@@ -6675,19 +6632,19 @@
         <v>20</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
@@ -6695,21 +6652,21 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -6718,20 +6675,18 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>125</v>
+        <v>306</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>126</v>
+        <v>307</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
         <v>20</v>
@@ -6780,19 +6735,19 @@
         <v>20</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>210</v>
+        <v>305</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
@@ -6800,45 +6755,45 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>214</v>
+        <v>311</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>128</v>
+        <v>312</v>
       </c>
       <c r="P51" t="s" s="2">
-        <v>134</v>
+        <v>313</v>
       </c>
       <c r="Q51" t="s" s="2">
         <v>20</v>
@@ -6863,13 +6818,13 @@
         <v>20</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="AB51" t="s" s="2">
         <v>20</v>
@@ -6887,19 +6842,19 @@
         <v>20</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>215</v>
+        <v>309</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52">
@@ -6907,10 +6862,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -6930,19 +6885,21 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>320</v>
+        <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="Q52" t="s" s="2">
         <v>20</v>
       </c>
@@ -6966,13 +6923,13 @@
         <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="AB52" t="s" s="2">
         <v>20</v>
@@ -6990,7 +6947,7 @@
         <v>20</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>73</v>
@@ -7010,10 +6967,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7039,16 +6996,16 @@
         <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="O53" t="s" s="2">
+      <c r="P53" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>20</v>
@@ -7073,13 +7030,13 @@
         <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>20</v>
@@ -7097,7 +7054,7 @@
         <v>20</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>73</v>
@@ -7117,10 +7074,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7131,7 +7088,7 @@
         <v>73</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
@@ -7146,14 +7103,16 @@
         <v>137</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="P54" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="Q54" t="s" s="2">
         <v>20</v>
@@ -7178,14 +7137,14 @@
         <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="Z54" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AA54" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AA54" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AB54" t="s" s="2">
         <v>20</v>
       </c>
@@ -7202,13 +7161,13 @@
         <v>20</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>20</v>
@@ -7222,10 +7181,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7245,22 +7204,22 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="O55" t="s" s="2">
+      <c r="P55" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>20</v>
@@ -7285,13 +7244,13 @@
         <v>20</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
         <v>20</v>
@@ -7309,7 +7268,7 @@
         <v>20</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>73</v>
@@ -7318,7 +7277,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>93</v>
@@ -7329,10 +7288,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7343,7 +7302,7 @@
         <v>73</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -7355,19 +7314,17 @@
         <v>20</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N56" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>20</v>
@@ -7392,13 +7349,13 @@
         <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
         <v>20</v>
@@ -7416,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>20</v>
@@ -7436,10 +7393,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -7462,19 +7419,19 @@
         <v>82</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="P57" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>20</v>
@@ -7523,7 +7480,7 @@
         <v>20</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>73</v>
@@ -7532,7 +7489,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>93</v>
@@ -7543,10 +7500,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -7557,7 +7514,7 @@
         <v>73</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -7569,13 +7526,13 @@
         <v>20</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7628,13 +7585,13 @@
         <v>20</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>20</v>
@@ -7648,10 +7605,10 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -7671,23 +7628,19 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>359</v>
+        <v>172</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>360</v>
+        <v>191</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
         <v>20</v>
       </c>
@@ -7735,7 +7688,7 @@
         <v>20</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>358</v>
+        <v>193</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>73</v>
@@ -7744,10 +7697,10 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -7755,14 +7708,14 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
@@ -7781,18 +7734,18 @@
         <v>20</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>365</v>
+        <v>126</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
         <v>20</v>
       </c>
@@ -7840,7 +7793,7 @@
         <v>20</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>364</v>
+        <v>196</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>73</v>
@@ -7852,7 +7805,7 @@
         <v>20</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61">
@@ -7860,42 +7813,46 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q61" t="s" s="2">
         <v>20</v>
       </c>
@@ -7943,19 +7900,19 @@
         <v>20</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62">
@@ -7963,21 +7920,21 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>20</v>
@@ -7989,17 +7946,15 @@
         <v>20</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>126</v>
+        <v>358</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
         <v>20</v>
@@ -8048,19 +8003,19 @@
         <v>20</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>210</v>
+        <v>357</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63">
@@ -8068,45 +8023,45 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>213</v>
+        <v>362</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>214</v>
+        <v>363</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>128</v>
+        <v>364</v>
       </c>
       <c r="P63" t="s" s="2">
-        <v>134</v>
+        <v>365</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>20</v>
@@ -8155,228 +8110,18 @@
         <v>20</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>215</v>
+        <v>360</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="D64" s="2"/>
-      <c r="E64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="F64" s="2"/>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="R64" s="2"/>
-      <c r="S64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="D65" s="2"/>
-      <c r="E65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="F65" s="2"/>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="R65" s="2"/>
-      <c r="S65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK65" t="s" s="2">
         <v>93</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T18:07:37+00:00</t>
+    <t>2026-05-16T09:46:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.12</t>
+    <t>0.0.13</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T09:46:24+00:00</t>
+    <t>2026-05-16T09:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
